--- a/tracker-nl.xlsx
+++ b/tracker-nl.xlsx
@@ -12,6 +12,7 @@
     <sheet name="Weekplan" sheetId="2" state="visible" r:id="rId4"/>
     <sheet name="Gewicht" sheetId="3" state="visible" r:id="rId5"/>
     <sheet name="Boodschappen" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="Recepten" sheetId="5" state="visible" r:id="rId7"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -23,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="371" uniqueCount="235">
   <si>
     <t xml:space="preserve">H</t>
   </si>
@@ -223,15 +224,33 @@
     <t xml:space="preserve">Notitie</t>
   </si>
   <si>
+    <t xml:space="preserve">BMI-TOOL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lengte (cm)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">← vul in</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Laatste gewicht (kg)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BMI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Categorie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BMI = gewicht ÷ lengte². Ruwe maat (spiermassa telt niet mee). Onder 18,5 = ondergewicht — dan niet verder afvallen.</t>
+  </si>
+  <si>
     <t xml:space="preserve">BOODSCHAPPEN</t>
   </si>
   <si>
     <t xml:space="preserve">Je weeklijst, per categorie. Vink af wat je in huis hebt.</t>
   </si>
   <si>
-    <t xml:space="preserve">Categorie</t>
-  </si>
-  <si>
     <t xml:space="preserve">Product</t>
   </si>
   <si>
@@ -290,6 +309,426 @@
   </si>
   <si>
     <t xml:space="preserve">Pasta 500g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RECEPTEN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10 kok-recepten met macro's en bereiding. Macro's zijn schattingen voor de genoemde hoeveelheden.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hartige Havermout met Ei</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ontbijt · Fibermaxxing / Herstel   —   420 kcal · 22g P · 42g C · 16g F · 9g vezels</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INGREDIËNTEN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Havermout</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50 g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vetarme bouillon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">150 ml</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verse spinazie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100 g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ei (gepocheerd)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 (50 g)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pompoenpitten</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15 g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BEREIDING</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Breng de bouillon in een steelpan tegen de kook aan.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roer de havermout erdoor en kook 4–5 min, al roerend, tot romig.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Schep de laatste minuut de spinazie erdoor tot net geslonken; breng op smaak.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pocheer ondertussen het ei ~3 min in zacht kokend water met een scheutje azijn.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Schep de havermout in een kom, leg het ei erop, strooi de pompoenpitten erover en wat peper.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vegan Linzen-Kikkererwten Curry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Diner · Plantaardig / Spieropbouw   —   510 kcal · 26g P · 58g C · 15g F · 14g vezels</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linzen (uit blik)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kikkererwten (uit blik)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tomatenblokjes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">150 g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lichte kokosmelk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50 ml</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Boerenkool</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30 g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Currykruiden</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verwarm een scheutje olie; rooster de currykruiden ~30 sec tot ze geuren.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Voeg de tomatenblokjes toe en laat 3–4 min inkoken.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roer de uitgelekte linzen en kikkererwten erdoor; laat 5 min pruttelen.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Giet de kokosmelk erbij, voeg de boerenkool toe en kook 2–3 min tot de kool zacht is.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Breng op smaak met zout; maak af met citroen of koriander. Serveer zo of met rijst.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matcha Protein Overnight Oats</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ontbijt · Focus / Pre-workout   —   460 kcal · 32g P · 48g C · 12g F · 8g vezels</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45 g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vanille-eiwitpoeder</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matchapoeder</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chiazaad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10 g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amandelmelk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Klop in een pot de amandelmelk met het eiwitpoeder en de matcha glad.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roer de havermout en het chiazaad erdoor.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sluit af en zet een nacht in de koelkast (minimaal 4 uur).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roer 's ochtends door; verdun met een scheutje melk als het te dik is. Top met fruit naar wens.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zalm &amp; Quinoa Clean Bowl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Diner · Clean label / Omega-3   —   580 kcal · 38g P · 45g C · 22g F · 7g vezels</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quinoa (droog)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60 g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zalmfilet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">125 g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Broccoli (gestoomd)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Edamameboontjes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Olijfolie + citroen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spoel de quinoa en kook in dubbele hoeveelheid water 12–15 min tot gaar; laat afgedekt rusten.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Breng de zalm op smaak en bak met de velkant naar beneden 3–4 min, draai dan 2 min (of oven 200°C ~12 min).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stoom de broccoli en edamame 4–5 min tot fris en net gaar.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Klop de olijfolie met het citroensap, zout en peper.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bouw de bowl met quinoa, broccoli en edamame; verdeel de zalm erover en besprenkel met dressing.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tempeh &amp; Broccoli Stir-Fry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Diner · Plantaardig / Darmflora   —   490 kcal · 28g P · 35g C · 21g F · 10g vezels</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tempeh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120 g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Broccoliroosjes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paprika</t>
+  </si>
+  <si>
+    <t xml:space="preserve">75 g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zilvervliesrijst (droog)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tamari, gember, knoflook</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kook de zilvervliesrijst (ca. 25 min) en houd warm.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Snijd de tempeh in blokjes en bak in een hete pan met wat olie goudbruin rondom.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Voeg broccoli en paprika toe; roerbak 4–5 min, met een scheutje water om te stomen.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Voeg geraspte gember en knoflook toe (30 sec), dan de tamari; schep om.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Serveer over de rijst.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ashwagandha Herstel Shake</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Snack · Adaptogenen / Rust   —   340 kcal · 26g P · 28g C · 8g F · 6g vezels</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bevroren banaan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eiwitpoeder</t>
+  </si>
+  <si>
+    <t xml:space="preserve">250 ml</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amandelpasta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ashwagandhapoeder</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Doe alles in een blender.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mix 30–45 sec tot glad en dik.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verdun met wat melk of maak dikker met ijs naar smaak. Direct drinken.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hüttenkäse &amp; Avocado Toast</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ontbijt · Snel eiwit / Gezonde vetten   —   390 kcal · 24g P · 30g C · 17g F · 8g vezels</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Volkoren-/zuurdesembrood</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70 g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hüttenkäse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Avocado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chili, peper, zout</t>
+  </si>
+  <si>
+    <t xml:space="preserve">naar smaak</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rooster het brood naar wens.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Smeer de hüttenkäse over het warme brood.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prak of snijd de avocado erop.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maak af met chilivlokken, zout en peper, en een kneepje citroen naar wens.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kip &amp; Zoete Aardappel Traybake</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Diner · Clean label / Duursport   —   540 kcal · 42g P · 52g C · 12g F · 8g vezels</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kipfilet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zoete aardappel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">200 g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aspergepunten</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Olijfolie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12 g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paprika, zout, rozemarijn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verwarm de oven op 200°C. Snijd de zoete aardappel in blokjes en meng met de helft van de olie, paprikapoeder en zout.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rooster de zoete aardappel 15 min op een bakplaat.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wrijf de kip in met de rest van de olie en de rozemarijn; leg op de plaat en rooster 15 min.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Voeg de asperges toe en rooster nog 8–10 min, tot de kip 74°C is.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Laat 3 min rusten en serveer.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chiapudding met Blauwe Bessen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Snack · Fibermaxxing / Antioxidanten   —   310 kcal · 15g P · 22g C · 14g F · 11g vezels</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25 g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lupinemeel / eiwitpoeder</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plantaardige melk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blauwe bessen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kaneel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Klop de plantaardige melk met het lupinemeel/eiwitpoeder en kaneel.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roer het chiazaad erdoor; wacht 5 min en roer opnieuw tegen klontjes.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zet 2 uur of een nacht in de koelkast tot het is opgesteven.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Top met de blauwe bessen voor het serveren.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eiwitrijke Proteïne Pannenkoeken</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ontbijt · Spierherstel / Klassieker   —   430 kcal · 35g P · 38g C · 9g F · 5g vezels</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Havermeel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40 g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Whey- of erwteneiwit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ei</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Magere melk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100 ml</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Klop het havermeel, eiwitpoeder, ei en melk tot een glad beslag; laat 5 min rusten.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verwarm een anti-aanbakpan op middelhoog met wat spray-olie.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Schep kleine pannenkoekjes; bak tot er belletjes komen (~1–2 min), draai om en bak 1 min verder.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stapel en top met fruit of yoghurt naar wens.</t>
   </si>
 </sst>
 </file>
@@ -298,17 +737,17 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="10">
     <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="General"/>
-    <numFmt numFmtId="166" formatCode="0.0&quot; kg&quot;"/>
-    <numFmt numFmtId="167" formatCode="\+0.0&quot; kg&quot;;\-0.0&quot; kg&quot;;0.0&quot; kg&quot;"/>
-    <numFmt numFmtId="168" formatCode="#,##0&quot; kcal&quot;"/>
-    <numFmt numFmtId="169" formatCode="#,##0"/>
-    <numFmt numFmtId="170" formatCode="0&quot; g&quot;"/>
+    <numFmt numFmtId="165" formatCode="0.0&quot; kg&quot;"/>
+    <numFmt numFmtId="166" formatCode="\+0.0&quot; kg&quot;;\-0.0&quot; kg&quot;;0.0&quot; kg&quot;"/>
+    <numFmt numFmtId="167" formatCode="#,##0&quot; kcal&quot;"/>
+    <numFmt numFmtId="168" formatCode="#,##0"/>
+    <numFmt numFmtId="169" formatCode="0&quot; g&quot;"/>
+    <numFmt numFmtId="170" formatCode="0.0"/>
     <numFmt numFmtId="171" formatCode="dd\-mm\-yyyy"/>
-    <numFmt numFmtId="172" formatCode="0.0"/>
-    <numFmt numFmtId="173" formatCode="\+0.0;\-0.0"/>
+    <numFmt numFmtId="172" formatCode="\+0.0;\-0.0"/>
+    <numFmt numFmtId="173" formatCode="General"/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="37">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -479,8 +918,69 @@
       <charset val="1"/>
     </font>
     <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
       <sz val="10"/>
       <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <color rgb="FF1F4E79"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF8C8C8C"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="13"/>
+      <color rgb="FFE8321E"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -492,8 +992,39 @@
       <family val="0"/>
       <charset val="1"/>
     </font>
+    <font>
+      <b val="true"/>
+      <sz val="14"/>
+      <color rgb="FF0A0A0A"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="12"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF404040"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FF0A0A0A"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -536,8 +1067,14 @@
         <bgColor rgb="FFFAFAFA"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF4CC"/>
+        <bgColor rgb="FFFFF0ED"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="13">
+  <borders count="14">
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
@@ -701,6 +1238,21 @@
       </bottom>
       <diagonal/>
     </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thin">
+        <color rgb="FFD9D9D9"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD9D9D9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="20">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -727,11 +1279,15 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="59">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -744,10 +1300,6 @@
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -756,11 +1308,11 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="8" fillId="3" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="8" fillId="3" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="9" fillId="3" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="9" fillId="3" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -768,15 +1320,15 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="8" fillId="3" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="8" fillId="3" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -796,7 +1348,7 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -804,7 +1356,7 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="16" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="16" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -820,23 +1372,23 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="5" fillId="3" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="5" fillId="3" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -844,7 +1396,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -852,7 +1404,7 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="7" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="22" fillId="7" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -860,11 +1412,15 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="23" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="171" fontId="22" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="172" fontId="23" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="170" fontId="24" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -872,20 +1428,92 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="22" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="25" fillId="0" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="26" fillId="8" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="24" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="172" fontId="22" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="173" fontId="28" fillId="0" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="29" fillId="3" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="30" fillId="0" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="31" fillId="0" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="32" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="30" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="34" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="35" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -917,7 +1545,7 @@
       <rgbColor rgb="FF878787"/>
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFFFF0ED"/>
+      <rgbColor rgb="FFFFF4CC"/>
       <rgbColor rgb="FFF6F6F6"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF6A52"/>
@@ -934,11 +1562,11 @@
       <rgbColor rgb="FF00CCFF"/>
       <rgbColor rgb="FFE6E6E6"/>
       <rgbColor rgb="FFFAFAFA"/>
-      <rgbColor rgb="FFFBFBFB"/>
+      <rgbColor rgb="FFFFF0ED"/>
       <rgbColor rgb="FF99CCFF"/>
       <rgbColor rgb="FFFF99CC"/>
       <rgbColor rgb="FFCC99FF"/>
-      <rgbColor rgb="FFFFCC99"/>
+      <rgbColor rgb="FFFBFBFB"/>
       <rgbColor rgb="FF3366FF"/>
       <rgbColor rgb="FF33CCCC"/>
       <rgbColor rgb="FF99CC00"/>
@@ -950,11 +1578,11 @@
       <rgbColor rgb="FF003366"/>
       <rgbColor rgb="FF1F9D55"/>
       <rgbColor rgb="FF0A0A0A"/>
-      <rgbColor rgb="FF333300"/>
+      <rgbColor rgb="FF444444"/>
       <rgbColor rgb="FF993300"/>
       <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FF333399"/>
-      <rgbColor rgb="FF444444"/>
+      <rgbColor rgb="FF1F4E79"/>
+      <rgbColor rgb="FF404040"/>
     </indexedColors>
   </colors>
 </styleSheet>
@@ -1000,22 +1628,26 @@
           </c:marker>
           <c:dLbls>
             <c:txPr>
-              <a:bodyPr wrap="none"/>
+              <a:bodyPr wrap="square"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
                   <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
               </a:p>
             </c:txPr>
+            <c:dLblPos val="r"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
-            <c:separator> </c:separator>
+            <c:separator>; </c:separator>
             <c:showLeaderLines val="1"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
@@ -1155,17 +1787,17 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="97164522"/>
-        <c:axId val="88282121"/>
+        <c:axId val="19874119"/>
+        <c:axId val="24448832"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="97164522"/>
+        <c:axId val="19874119"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
-        <c:numFmt formatCode="dd\-mm\-yyyy" sourceLinked="1"/>
+        <c:numFmt formatCode="dd\-mm\-yyyy" sourceLinked="0"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -1191,7 +1823,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="88282121"/>
+        <c:crossAx val="24448832"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1199,13 +1831,13 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="88282121"/>
+        <c:axId val="24448832"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
-        <c:numFmt formatCode="0.0" sourceLinked="1"/>
+        <c:numFmt formatCode="0.0" sourceLinked="0"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -1231,7 +1863,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="97164522"/>
+        <c:crossAx val="19874119"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1270,9 +1902,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>78120</xdr:colOff>
+      <xdr:colOff>77400</xdr:colOff>
       <xdr:row>14</xdr:row>
-      <xdr:rowOff>97920</xdr:rowOff>
+      <xdr:rowOff>97200</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -1281,7 +1913,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="0" y="1743120"/>
-        <a:ext cx="4139640" cy="1907640"/>
+        <a:ext cx="4138920" cy="1906920"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -1478,50 +2110,50 @@
   <dimension ref="A1:N20"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="1" style="0" width="9.6"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="14" min="14" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="1" style="1" width="9.6"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="14" min="14" style="1" width="13"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="I1" s="3" t="s">
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="I1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
-      <c r="N1" s="4" t="n">
+      <c r="J1" s="4"/>
+      <c r="K1" s="4"/>
+      <c r="L1" s="4"/>
+      <c r="N1" s="1" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(Gewicht!$B$4:$B$30&lt;&gt;""),Gewicht!$B$4:$B$30),"")</f>
         <v>87</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="I2" s="3"/>
-      <c r="J2" s="3"/>
-      <c r="K2" s="3"/>
-      <c r="L2" s="3"/>
-      <c r="N2" s="4" t="n">
+      <c r="A2" s="2"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="I2" s="4"/>
+      <c r="J2" s="4"/>
+      <c r="K2" s="4"/>
+      <c r="L2" s="4"/>
+      <c r="N2" s="1" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(Gewicht!$C$4:$C$30&lt;&gt;""),Gewicht!$C$4:$C$30),"")</f>
         <v>-0.200000000000003</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="N3" s="0" t="n">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="N3" s="1" t="n">
         <f aca="false">IF(AND(N1&lt;&gt;"",N2&lt;&gt;""),N2/N1,"")</f>
         <v>-0.00229885057471268</v>
       </c>
@@ -1589,7 +2221,7 @@
       <c r="L6" s="10"/>
     </row>
     <row r="7" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="11" t="s">
         <v>7</v>
       </c>
@@ -1706,7 +2338,7 @@
       <c r="L16" s="20"/>
     </row>
     <row r="17" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="11" t="s">
         <v>15</v>
       </c>
@@ -1826,17 +2458,17 @@
   <dimension ref="A1:I31"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="40"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="9" min="9" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="1" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="9" min="9" style="1" width="14"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="26" t="s">
         <v>19</v>
       </c>
@@ -1848,7 +2480,7 @@
       <c r="G1" s="26"/>
       <c r="H1" s="26"/>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="27" t="s">
         <v>20</v>
       </c>
@@ -1860,7 +2492,7 @@
       <c r="G2" s="27"/>
       <c r="H2" s="27"/>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="28" t="s">
         <v>21</v>
       </c>
@@ -1885,11 +2517,11 @@
       <c r="H3" s="28" t="s">
         <v>28</v>
       </c>
-      <c r="I3" s="4" t="s">
+      <c r="I3" s="1" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="29" t="s">
         <v>9</v>
       </c>
@@ -1914,12 +2546,12 @@
       <c r="H4" s="30" t="n">
         <v>18</v>
       </c>
-      <c r="I4" s="0" t="str">
+      <c r="I4" s="1" t="str">
         <f aca="false">$A4&amp;"|"&amp;$B4</f>
         <v>Ma|Ontbijt</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="29" t="s">
         <v>9</v>
       </c>
@@ -1944,12 +2576,12 @@
       <c r="H5" s="30" t="n">
         <v>12</v>
       </c>
-      <c r="I5" s="0" t="str">
+      <c r="I5" s="1" t="str">
         <f aca="false">$A5&amp;"|"&amp;$B5</f>
         <v>Ma|Lunch</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="29" t="s">
         <v>9</v>
       </c>
@@ -1974,12 +2606,12 @@
       <c r="H6" s="30" t="n">
         <v>16</v>
       </c>
-      <c r="I6" s="0" t="str">
+      <c r="I6" s="1" t="str">
         <f aca="false">$A6&amp;"|"&amp;$B6</f>
         <v>Ma|Diner</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="29" t="s">
         <v>9</v>
       </c>
@@ -2004,12 +2636,12 @@
       <c r="H7" s="30" t="n">
         <v>14</v>
       </c>
-      <c r="I7" s="0" t="str">
+      <c r="I7" s="1" t="str">
         <f aca="false">$A7&amp;"|"&amp;$B7</f>
         <v>Ma|Snack</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="31" t="s">
         <v>38</v>
       </c>
@@ -2034,12 +2666,12 @@
       <c r="H8" s="32" t="n">
         <v>6</v>
       </c>
-      <c r="I8" s="0" t="str">
+      <c r="I8" s="1" t="str">
         <f aca="false">$A8&amp;"|"&amp;$B8</f>
         <v>Di|Ontbijt</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="31" t="s">
         <v>38</v>
       </c>
@@ -2064,12 +2696,12 @@
       <c r="H9" s="32" t="n">
         <v>10</v>
       </c>
-      <c r="I9" s="0" t="str">
+      <c r="I9" s="1" t="str">
         <f aca="false">$A9&amp;"|"&amp;$B9</f>
         <v>Di|Lunch</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="31" t="s">
         <v>38</v>
       </c>
@@ -2094,12 +2726,12 @@
       <c r="H10" s="32" t="n">
         <v>26</v>
       </c>
-      <c r="I10" s="0" t="str">
+      <c r="I10" s="1" t="str">
         <f aca="false">$A10&amp;"|"&amp;$B10</f>
         <v>Di|Diner</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="31" t="s">
         <v>38</v>
       </c>
@@ -2124,12 +2756,12 @@
       <c r="H11" s="32" t="n">
         <v>7</v>
       </c>
-      <c r="I11" s="0" t="str">
+      <c r="I11" s="1" t="str">
         <f aca="false">$A11&amp;"|"&amp;$B11</f>
         <v>Di|Snack</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="29" t="s">
         <v>47</v>
       </c>
@@ -2154,12 +2786,12 @@
       <c r="H12" s="30" t="n">
         <v>10</v>
       </c>
-      <c r="I12" s="0" t="str">
+      <c r="I12" s="1" t="str">
         <f aca="false">$A12&amp;"|"&amp;$B12</f>
         <v>Wo|Ontbijt</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="29" t="s">
         <v>47</v>
       </c>
@@ -2184,12 +2816,12 @@
       <c r="H13" s="30" t="n">
         <v>30</v>
       </c>
-      <c r="I13" s="0" t="str">
+      <c r="I13" s="1" t="str">
         <f aca="false">$A13&amp;"|"&amp;$B13</f>
         <v>Wo|Lunch</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="29" t="s">
         <v>47</v>
       </c>
@@ -2214,12 +2846,12 @@
       <c r="H14" s="30" t="n">
         <v>14</v>
       </c>
-      <c r="I14" s="0" t="str">
+      <c r="I14" s="1" t="str">
         <f aca="false">$A14&amp;"|"&amp;$B14</f>
         <v>Wo|Diner</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="29" t="s">
         <v>47</v>
       </c>
@@ -2244,12 +2876,12 @@
       <c r="H15" s="30" t="n">
         <v>2</v>
       </c>
-      <c r="I15" s="0" t="str">
+      <c r="I15" s="1" t="str">
         <f aca="false">$A15&amp;"|"&amp;$B15</f>
         <v>Wo|Snack</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="31" t="s">
         <v>56</v>
       </c>
@@ -2274,12 +2906,12 @@
       <c r="H16" s="32" t="n">
         <v>18</v>
       </c>
-      <c r="I16" s="0" t="str">
+      <c r="I16" s="1" t="str">
         <f aca="false">$A16&amp;"|"&amp;$B16</f>
         <v>Do|Ontbijt</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="31" t="s">
         <v>56</v>
       </c>
@@ -2304,12 +2936,12 @@
       <c r="H17" s="32" t="n">
         <v>12</v>
       </c>
-      <c r="I17" s="0" t="str">
+      <c r="I17" s="1" t="str">
         <f aca="false">$A17&amp;"|"&amp;$B17</f>
         <v>Do|Lunch</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="31" t="s">
         <v>56</v>
       </c>
@@ -2334,12 +2966,12 @@
       <c r="H18" s="32" t="n">
         <v>16</v>
       </c>
-      <c r="I18" s="0" t="str">
+      <c r="I18" s="1" t="str">
         <f aca="false">$A18&amp;"|"&amp;$B18</f>
         <v>Do|Diner</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="31" t="s">
         <v>56</v>
       </c>
@@ -2364,12 +2996,12 @@
       <c r="H19" s="32" t="n">
         <v>14</v>
       </c>
-      <c r="I19" s="0" t="str">
+      <c r="I19" s="1" t="str">
         <f aca="false">$A19&amp;"|"&amp;$B19</f>
         <v>Do|Snack</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="29" t="s">
         <v>57</v>
       </c>
@@ -2394,12 +3026,12 @@
       <c r="H20" s="30" t="n">
         <v>6</v>
       </c>
-      <c r="I20" s="0" t="str">
+      <c r="I20" s="1" t="str">
         <f aca="false">$A20&amp;"|"&amp;$B20</f>
         <v>Vr|Ontbijt</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="29" t="s">
         <v>57</v>
       </c>
@@ -2424,12 +3056,12 @@
       <c r="H21" s="30" t="n">
         <v>10</v>
       </c>
-      <c r="I21" s="0" t="str">
+      <c r="I21" s="1" t="str">
         <f aca="false">$A21&amp;"|"&amp;$B21</f>
         <v>Vr|Lunch</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="29" t="s">
         <v>57</v>
       </c>
@@ -2454,12 +3086,12 @@
       <c r="H22" s="30" t="n">
         <v>26</v>
       </c>
-      <c r="I22" s="0" t="str">
+      <c r="I22" s="1" t="str">
         <f aca="false">$A22&amp;"|"&amp;$B22</f>
         <v>Vr|Diner</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="29" t="s">
         <v>57</v>
       </c>
@@ -2484,12 +3116,12 @@
       <c r="H23" s="30" t="n">
         <v>7</v>
       </c>
-      <c r="I23" s="0" t="str">
+      <c r="I23" s="1" t="str">
         <f aca="false">$A23&amp;"|"&amp;$B23</f>
         <v>Vr|Snack</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="31" t="s">
         <v>58</v>
       </c>
@@ -2514,12 +3146,12 @@
       <c r="H24" s="32" t="n">
         <v>10</v>
       </c>
-      <c r="I24" s="0" t="str">
+      <c r="I24" s="1" t="str">
         <f aca="false">$A24&amp;"|"&amp;$B24</f>
         <v>Za|Ontbijt</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="31" t="s">
         <v>58</v>
       </c>
@@ -2544,12 +3176,12 @@
       <c r="H25" s="32" t="n">
         <v>30</v>
       </c>
-      <c r="I25" s="0" t="str">
+      <c r="I25" s="1" t="str">
         <f aca="false">$A25&amp;"|"&amp;$B25</f>
         <v>Za|Lunch</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="31" t="s">
         <v>58</v>
       </c>
@@ -2574,12 +3206,12 @@
       <c r="H26" s="32" t="n">
         <v>14</v>
       </c>
-      <c r="I26" s="0" t="str">
+      <c r="I26" s="1" t="str">
         <f aca="false">$A26&amp;"|"&amp;$B26</f>
         <v>Za|Diner</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="31" t="s">
         <v>58</v>
       </c>
@@ -2604,12 +3236,12 @@
       <c r="H27" s="32" t="n">
         <v>2</v>
       </c>
-      <c r="I27" s="0" t="str">
+      <c r="I27" s="1" t="str">
         <f aca="false">$A27&amp;"|"&amp;$B27</f>
         <v>Za|Snack</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="29" t="s">
         <v>59</v>
       </c>
@@ -2634,12 +3266,12 @@
       <c r="H28" s="30" t="n">
         <v>18</v>
       </c>
-      <c r="I28" s="0" t="str">
+      <c r="I28" s="1" t="str">
         <f aca="false">$A28&amp;"|"&amp;$B28</f>
         <v>Zo|Ontbijt</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="29" t="s">
         <v>59</v>
       </c>
@@ -2664,12 +3296,12 @@
       <c r="H29" s="30" t="n">
         <v>12</v>
       </c>
-      <c r="I29" s="0" t="str">
+      <c r="I29" s="1" t="str">
         <f aca="false">$A29&amp;"|"&amp;$B29</f>
         <v>Zo|Lunch</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="29" t="s">
         <v>59</v>
       </c>
@@ -2694,12 +3326,12 @@
       <c r="H30" s="30" t="n">
         <v>16</v>
       </c>
-      <c r="I30" s="0" t="str">
+      <c r="I30" s="1" t="str">
         <f aca="false">$A30&amp;"|"&amp;$B30</f>
         <v>Zo|Diner</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="29" t="s">
         <v>59</v>
       </c>
@@ -2724,7 +3356,7 @@
       <c r="H31" s="30" t="n">
         <v>14</v>
       </c>
-      <c r="I31" s="0" t="str">
+      <c r="I31" s="1" t="str">
         <f aca="false">$A31&amp;"|"&amp;$B31</f>
         <v>Zo|Snack</v>
       </c>
@@ -2750,15 +3382,18 @@
     <tabColor rgb="FFD9D9D9"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D30"/>
+  <dimension ref="A1:H30"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="10"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="26" t="s">
         <v>60</v>
       </c>
@@ -2766,7 +3401,7 @@
       <c r="C1" s="26"/>
       <c r="D1" s="26"/>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="27" t="s">
         <v>61</v>
       </c>
@@ -2774,7 +3409,7 @@
       <c r="C2" s="27"/>
       <c r="D2" s="27"/>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="28" t="s">
         <v>62</v>
       </c>
@@ -2787,283 +3422,332 @@
       <c r="D3" s="28" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="33" t="n">
+      <c r="F3" s="33" t="s">
+        <v>66</v>
+      </c>
+      <c r="G3" s="33"/>
+      <c r="H3" s="33"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="34" t="n">
         <v>46271</v>
       </c>
-      <c r="B4" s="34" t="n">
+      <c r="B4" s="35" t="n">
         <v>88.6</v>
       </c>
       <c r="C4" s="30"/>
-      <c r="D4" s="35"/>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="33" t="n">
+      <c r="D4" s="36"/>
+      <c r="F4" s="37" t="s">
+        <v>67</v>
+      </c>
+      <c r="G4" s="38"/>
+      <c r="H4" s="39" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="34" t="n">
         <v>46278</v>
       </c>
-      <c r="B5" s="34" t="n">
+      <c r="B5" s="35" t="n">
         <v>88.2</v>
       </c>
-      <c r="C5" s="36" t="n">
+      <c r="C5" s="40" t="n">
         <f aca="false">IF(AND(B5&lt;&gt;"",B4&lt;&gt;""),B5-B4,"")</f>
         <v>-0.399999999999992</v>
       </c>
-      <c r="D5" s="35"/>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="33" t="n">
+      <c r="D5" s="36"/>
+      <c r="F5" s="37" t="s">
+        <v>69</v>
+      </c>
+      <c r="G5" s="41" t="n">
+        <f aca="false">IFERROR(LOOKUP(2,1/(B4:B30&lt;&gt;""),B4:B30),"")</f>
+        <v>87</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="34" t="n">
         <v>46285</v>
       </c>
-      <c r="B6" s="34" t="n">
+      <c r="B6" s="35" t="n">
         <v>88.4</v>
       </c>
-      <c r="C6" s="36" t="n">
+      <c r="C6" s="40" t="n">
         <f aca="false">IF(AND(B6&lt;&gt;"",B5&lt;&gt;""),B6-B5,"")</f>
         <v>0.200000000000003</v>
       </c>
-      <c r="D6" s="35"/>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="33" t="n">
+      <c r="D6" s="36"/>
+      <c r="F6" s="42" t="s">
+        <v>70</v>
+      </c>
+      <c r="G6" s="43" t="str">
+        <f aca="false">IF(AND(G4&gt;0,G5&gt;0),ROUND(G5/(G4/100)^2,1),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="34" t="n">
         <v>46292</v>
       </c>
-      <c r="B7" s="34" t="n">
+      <c r="B7" s="35" t="n">
         <v>87.9</v>
       </c>
-      <c r="C7" s="36" t="n">
+      <c r="C7" s="40" t="n">
         <f aca="false">IF(AND(B7&lt;&gt;"",B6&lt;&gt;""),B7-B6,"")</f>
         <v>-0.5</v>
       </c>
-      <c r="D7" s="35"/>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="33" t="n">
+      <c r="D7" s="36"/>
+      <c r="F7" s="37" t="s">
+        <v>71</v>
+      </c>
+      <c r="G7" s="44" t="str">
+        <f aca="false">IF(G6="","",IF(G6&lt;18.5,"Ondergewicht",IF(G6&lt;25,"Gezond",IF(G6&lt;30,"Overgewicht","Obesitas"))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="34" t="n">
         <v>46299</v>
       </c>
-      <c r="B8" s="34" t="n">
+      <c r="B8" s="35" t="n">
         <v>87.6</v>
       </c>
-      <c r="C8" s="36" t="n">
+      <c r="C8" s="40" t="n">
         <f aca="false">IF(AND(B8&lt;&gt;"",B7&lt;&gt;""),B8-B7,"")</f>
         <v>-0.300000000000011</v>
       </c>
-      <c r="D8" s="35"/>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="33" t="n">
+      <c r="D8" s="36"/>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="34" t="n">
         <v>46306</v>
       </c>
-      <c r="B9" s="34" t="n">
+      <c r="B9" s="35" t="n">
         <v>87.7</v>
       </c>
-      <c r="C9" s="36" t="n">
+      <c r="C9" s="40" t="n">
         <f aca="false">IF(AND(B9&lt;&gt;"",B8&lt;&gt;""),B9-B8,"")</f>
         <v>0.100000000000009</v>
       </c>
-      <c r="D9" s="35"/>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="33" t="n">
+      <c r="D9" s="36"/>
+      <c r="F9" s="45" t="s">
+        <v>72</v>
+      </c>
+      <c r="G9" s="45"/>
+      <c r="H9" s="45"/>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="34" t="n">
         <v>46313</v>
       </c>
-      <c r="B10" s="34" t="n">
+      <c r="B10" s="35" t="n">
         <v>87.2</v>
       </c>
-      <c r="C10" s="36" t="n">
+      <c r="C10" s="40" t="n">
         <f aca="false">IF(AND(B10&lt;&gt;"",B9&lt;&gt;""),B10-B9,"")</f>
         <v>-0.5</v>
       </c>
-      <c r="D10" s="35"/>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="33" t="n">
+      <c r="D10" s="36"/>
+      <c r="F10" s="45"/>
+      <c r="G10" s="45"/>
+      <c r="H10" s="45"/>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="34" t="n">
         <v>46320</v>
       </c>
-      <c r="B11" s="34" t="n">
+      <c r="B11" s="35" t="n">
         <v>87</v>
       </c>
-      <c r="C11" s="36" t="n">
+      <c r="C11" s="40" t="n">
         <f aca="false">IF(AND(B11&lt;&gt;"",B10&lt;&gt;""),B11-B10,"")</f>
         <v>-0.200000000000003</v>
       </c>
-      <c r="D11" s="35"/>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D11" s="36"/>
+      <c r="F11" s="45"/>
+      <c r="G11" s="45"/>
+      <c r="H11" s="45"/>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="30"/>
-      <c r="B12" s="34"/>
-      <c r="C12" s="36" t="str">
+      <c r="B12" s="35"/>
+      <c r="C12" s="40" t="str">
         <f aca="false">IF(AND(B12&lt;&gt;"",B11&lt;&gt;""),B12-B11,"")</f>
         <v/>
       </c>
-      <c r="D12" s="35"/>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D12" s="36"/>
+      <c r="F12" s="45"/>
+      <c r="G12" s="45"/>
+      <c r="H12" s="45"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="30"/>
-      <c r="B13" s="34"/>
-      <c r="C13" s="36" t="str">
+      <c r="B13" s="35"/>
+      <c r="C13" s="40" t="str">
         <f aca="false">IF(AND(B13&lt;&gt;"",B12&lt;&gt;""),B13-B12,"")</f>
         <v/>
       </c>
-      <c r="D13" s="35"/>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D13" s="36"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="30"/>
-      <c r="B14" s="34"/>
-      <c r="C14" s="36" t="str">
+      <c r="B14" s="35"/>
+      <c r="C14" s="40" t="str">
         <f aca="false">IF(AND(B14&lt;&gt;"",B13&lt;&gt;""),B14-B13,"")</f>
         <v/>
       </c>
-      <c r="D14" s="35"/>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D14" s="36"/>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="30"/>
-      <c r="B15" s="34"/>
-      <c r="C15" s="36" t="str">
+      <c r="B15" s="35"/>
+      <c r="C15" s="40" t="str">
         <f aca="false">IF(AND(B15&lt;&gt;"",B14&lt;&gt;""),B15-B14,"")</f>
         <v/>
       </c>
-      <c r="D15" s="35"/>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D15" s="36"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="30"/>
-      <c r="B16" s="34"/>
-      <c r="C16" s="36" t="str">
+      <c r="B16" s="35"/>
+      <c r="C16" s="40" t="str">
         <f aca="false">IF(AND(B16&lt;&gt;"",B15&lt;&gt;""),B16-B15,"")</f>
         <v/>
       </c>
-      <c r="D16" s="35"/>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D16" s="36"/>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="30"/>
-      <c r="B17" s="34"/>
-      <c r="C17" s="36" t="str">
+      <c r="B17" s="35"/>
+      <c r="C17" s="40" t="str">
         <f aca="false">IF(AND(B17&lt;&gt;"",B16&lt;&gt;""),B17-B16,"")</f>
         <v/>
       </c>
-      <c r="D17" s="35"/>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D17" s="36"/>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="30"/>
-      <c r="B18" s="34"/>
-      <c r="C18" s="36" t="str">
+      <c r="B18" s="35"/>
+      <c r="C18" s="40" t="str">
         <f aca="false">IF(AND(B18&lt;&gt;"",B17&lt;&gt;""),B18-B17,"")</f>
         <v/>
       </c>
-      <c r="D18" s="35"/>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D18" s="36"/>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="30"/>
-      <c r="B19" s="34"/>
-      <c r="C19" s="36" t="str">
+      <c r="B19" s="35"/>
+      <c r="C19" s="40" t="str">
         <f aca="false">IF(AND(B19&lt;&gt;"",B18&lt;&gt;""),B19-B18,"")</f>
         <v/>
       </c>
-      <c r="D19" s="35"/>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D19" s="36"/>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="30"/>
-      <c r="B20" s="34"/>
-      <c r="C20" s="36" t="str">
+      <c r="B20" s="35"/>
+      <c r="C20" s="40" t="str">
         <f aca="false">IF(AND(B20&lt;&gt;"",B19&lt;&gt;""),B20-B19,"")</f>
         <v/>
       </c>
-      <c r="D20" s="35"/>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D20" s="36"/>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="30"/>
-      <c r="B21" s="34"/>
-      <c r="C21" s="36" t="str">
+      <c r="B21" s="35"/>
+      <c r="C21" s="40" t="str">
         <f aca="false">IF(AND(B21&lt;&gt;"",B20&lt;&gt;""),B21-B20,"")</f>
         <v/>
       </c>
-      <c r="D21" s="35"/>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D21" s="36"/>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="30"/>
-      <c r="B22" s="34"/>
-      <c r="C22" s="36" t="str">
+      <c r="B22" s="35"/>
+      <c r="C22" s="40" t="str">
         <f aca="false">IF(AND(B22&lt;&gt;"",B21&lt;&gt;""),B22-B21,"")</f>
         <v/>
       </c>
-      <c r="D22" s="35"/>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D22" s="36"/>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="30"/>
-      <c r="B23" s="34"/>
-      <c r="C23" s="36" t="str">
+      <c r="B23" s="35"/>
+      <c r="C23" s="40" t="str">
         <f aca="false">IF(AND(B23&lt;&gt;"",B22&lt;&gt;""),B23-B22,"")</f>
         <v/>
       </c>
-      <c r="D23" s="35"/>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D23" s="36"/>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="30"/>
-      <c r="B24" s="34"/>
-      <c r="C24" s="36" t="str">
+      <c r="B24" s="35"/>
+      <c r="C24" s="40" t="str">
         <f aca="false">IF(AND(B24&lt;&gt;"",B23&lt;&gt;""),B24-B23,"")</f>
         <v/>
       </c>
-      <c r="D24" s="35"/>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D24" s="36"/>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="30"/>
-      <c r="B25" s="34"/>
-      <c r="C25" s="36" t="str">
+      <c r="B25" s="35"/>
+      <c r="C25" s="40" t="str">
         <f aca="false">IF(AND(B25&lt;&gt;"",B24&lt;&gt;""),B25-B24,"")</f>
         <v/>
       </c>
-      <c r="D25" s="35"/>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D25" s="36"/>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="30"/>
-      <c r="B26" s="34"/>
-      <c r="C26" s="36" t="str">
+      <c r="B26" s="35"/>
+      <c r="C26" s="40" t="str">
         <f aca="false">IF(AND(B26&lt;&gt;"",B25&lt;&gt;""),B26-B25,"")</f>
         <v/>
       </c>
-      <c r="D26" s="35"/>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D26" s="36"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="30"/>
-      <c r="B27" s="34"/>
-      <c r="C27" s="36" t="str">
+      <c r="B27" s="35"/>
+      <c r="C27" s="40" t="str">
         <f aca="false">IF(AND(B27&lt;&gt;"",B26&lt;&gt;""),B27-B26,"")</f>
         <v/>
       </c>
-      <c r="D27" s="35"/>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D27" s="36"/>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="30"/>
-      <c r="B28" s="34"/>
-      <c r="C28" s="36" t="str">
+      <c r="B28" s="35"/>
+      <c r="C28" s="40" t="str">
         <f aca="false">IF(AND(B28&lt;&gt;"",B27&lt;&gt;""),B28-B27,"")</f>
         <v/>
       </c>
-      <c r="D28" s="35"/>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D28" s="36"/>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="30"/>
-      <c r="B29" s="34"/>
-      <c r="C29" s="36" t="str">
+      <c r="B29" s="35"/>
+      <c r="C29" s="40" t="str">
         <f aca="false">IF(AND(B29&lt;&gt;"",B28&lt;&gt;""),B29-B28,"")</f>
         <v/>
       </c>
-      <c r="D29" s="35"/>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D29" s="36"/>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="30"/>
-      <c r="B30" s="34"/>
-      <c r="C30" s="36" t="str">
+      <c r="B30" s="35"/>
+      <c r="C30" s="40" t="str">
         <f aca="false">IF(AND(B30&lt;&gt;"",B29&lt;&gt;""),B30-B29,"")</f>
         <v/>
       </c>
-      <c r="D30" s="35"/>
+      <c r="D30" s="36"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="4">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A2:D2"/>
+    <mergeCell ref="F3:H3"/>
+    <mergeCell ref="F9:H12"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -3084,171 +3768,171 @@
   <dimension ref="A1:D16"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="9"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="26" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="B1" s="26"/>
       <c r="C1" s="26"/>
       <c r="D1" s="26"/>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="27" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="B2" s="27"/>
       <c r="C2" s="27"/>
       <c r="D2" s="27"/>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="28" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B3" s="28" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="C3" s="28" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="D3" s="28" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="37" t="s">
-        <v>72</v>
+        <v>77</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="46" t="s">
+        <v>78</v>
       </c>
       <c r="B4" s="29" t="s">
-        <v>73</v>
-      </c>
-      <c r="C4" s="38"/>
-      <c r="D4" s="39"/>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="37" t="s">
-        <v>72</v>
+        <v>79</v>
+      </c>
+      <c r="C4" s="47"/>
+      <c r="D4" s="48"/>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="46" t="s">
+        <v>78</v>
       </c>
       <c r="B5" s="29" t="s">
-        <v>74</v>
-      </c>
-      <c r="C5" s="38"/>
-      <c r="D5" s="39"/>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="37" t="s">
-        <v>72</v>
+        <v>80</v>
+      </c>
+      <c r="C5" s="47"/>
+      <c r="D5" s="48"/>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="46" t="s">
+        <v>78</v>
       </c>
       <c r="B6" s="29" t="s">
-        <v>75</v>
-      </c>
-      <c r="C6" s="38"/>
-      <c r="D6" s="39"/>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="37" t="s">
-        <v>72</v>
+        <v>81</v>
+      </c>
+      <c r="C6" s="47"/>
+      <c r="D6" s="48"/>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="46" t="s">
+        <v>78</v>
       </c>
       <c r="B7" s="29" t="s">
-        <v>76</v>
-      </c>
-      <c r="C7" s="38"/>
-      <c r="D7" s="39"/>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="37" t="s">
-        <v>77</v>
+        <v>82</v>
+      </c>
+      <c r="C7" s="47"/>
+      <c r="D7" s="48"/>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="46" t="s">
+        <v>83</v>
       </c>
       <c r="B8" s="29" t="s">
-        <v>78</v>
-      </c>
-      <c r="C8" s="38"/>
-      <c r="D8" s="39"/>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="37" t="s">
-        <v>77</v>
+        <v>84</v>
+      </c>
+      <c r="C8" s="47"/>
+      <c r="D8" s="48"/>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="46" t="s">
+        <v>83</v>
       </c>
       <c r="B9" s="29" t="s">
-        <v>79</v>
-      </c>
-      <c r="C9" s="38"/>
-      <c r="D9" s="39"/>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="37" t="s">
-        <v>77</v>
+        <v>85</v>
+      </c>
+      <c r="C9" s="47"/>
+      <c r="D9" s="48"/>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="46" t="s">
+        <v>83</v>
       </c>
       <c r="B10" s="29" t="s">
-        <v>80</v>
-      </c>
-      <c r="C10" s="38"/>
-      <c r="D10" s="39"/>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="37" t="s">
-        <v>81</v>
+        <v>86</v>
+      </c>
+      <c r="C10" s="47"/>
+      <c r="D10" s="48"/>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="46" t="s">
+        <v>87</v>
       </c>
       <c r="B11" s="29" t="s">
-        <v>82</v>
-      </c>
-      <c r="C11" s="38"/>
-      <c r="D11" s="39"/>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="37" t="s">
-        <v>81</v>
+        <v>88</v>
+      </c>
+      <c r="C11" s="47"/>
+      <c r="D11" s="48"/>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="46" t="s">
+        <v>87</v>
       </c>
       <c r="B12" s="29" t="s">
-        <v>83</v>
-      </c>
-      <c r="C12" s="38"/>
-      <c r="D12" s="39"/>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="37" t="s">
-        <v>81</v>
+        <v>89</v>
+      </c>
+      <c r="C12" s="47"/>
+      <c r="D12" s="48"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="46" t="s">
+        <v>87</v>
       </c>
       <c r="B13" s="29" t="s">
-        <v>84</v>
-      </c>
-      <c r="C13" s="38"/>
-      <c r="D13" s="39"/>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="37" t="s">
-        <v>85</v>
+        <v>90</v>
+      </c>
+      <c r="C13" s="47"/>
+      <c r="D13" s="48"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="46" t="s">
+        <v>91</v>
       </c>
       <c r="B14" s="29" t="s">
-        <v>86</v>
-      </c>
-      <c r="C14" s="38"/>
-      <c r="D14" s="39"/>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="37" t="s">
-        <v>85</v>
+        <v>92</v>
+      </c>
+      <c r="C14" s="47"/>
+      <c r="D14" s="48"/>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="46" t="s">
+        <v>91</v>
       </c>
       <c r="B15" s="29" t="s">
-        <v>87</v>
-      </c>
-      <c r="C15" s="38"/>
-      <c r="D15" s="39"/>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="37" t="s">
-        <v>85</v>
+        <v>93</v>
+      </c>
+      <c r="C15" s="47"/>
+      <c r="D15" s="48"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="46" t="s">
+        <v>91</v>
       </c>
       <c r="B16" s="29" t="s">
-        <v>88</v>
-      </c>
-      <c r="C16" s="38"/>
-      <c r="D16" s="39"/>
+        <v>94</v>
+      </c>
+      <c r="C16" s="47"/>
+      <c r="D16" s="48"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -3263,4 +3947,1319 @@
     <oddFooter/>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:D145"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="12"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="49" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="50" t="s">
+        <v>96</v>
+      </c>
+      <c r="B2" s="50"/>
+      <c r="C2" s="50"/>
+      <c r="D2" s="50"/>
+    </row>
+    <row r="4" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="52" t="s">
+        <v>97</v>
+      </c>
+      <c r="C4" s="52"/>
+      <c r="D4" s="52"/>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="53" t="s">
+        <v>98</v>
+      </c>
+      <c r="B5" s="53"/>
+      <c r="C5" s="53"/>
+      <c r="D5" s="53"/>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="54" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B7" s="55" t="s">
+        <v>100</v>
+      </c>
+      <c r="C7" s="55"/>
+      <c r="D7" s="56" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B8" s="55" t="s">
+        <v>102</v>
+      </c>
+      <c r="C8" s="55"/>
+      <c r="D8" s="56" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B9" s="55" t="s">
+        <v>104</v>
+      </c>
+      <c r="C9" s="55"/>
+      <c r="D9" s="56" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B10" s="55" t="s">
+        <v>106</v>
+      </c>
+      <c r="C10" s="55"/>
+      <c r="D10" s="56" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B11" s="55" t="s">
+        <v>108</v>
+      </c>
+      <c r="C11" s="55"/>
+      <c r="D11" s="56" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="54" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="B13" s="58" t="s">
+        <v>111</v>
+      </c>
+      <c r="C13" s="58"/>
+      <c r="D13" s="58"/>
+    </row>
+    <row r="14" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="57" t="n">
+        <v>2</v>
+      </c>
+      <c r="B14" s="58" t="s">
+        <v>112</v>
+      </c>
+      <c r="C14" s="58"/>
+      <c r="D14" s="58"/>
+    </row>
+    <row r="15" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="57" t="n">
+        <v>3</v>
+      </c>
+      <c r="B15" s="58" t="s">
+        <v>113</v>
+      </c>
+      <c r="C15" s="58"/>
+      <c r="D15" s="58"/>
+    </row>
+    <row r="16" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="57" t="n">
+        <v>4</v>
+      </c>
+      <c r="B16" s="58" t="s">
+        <v>114</v>
+      </c>
+      <c r="C16" s="58"/>
+      <c r="D16" s="58"/>
+    </row>
+    <row r="17" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="57" t="n">
+        <v>5</v>
+      </c>
+      <c r="B17" s="58" t="s">
+        <v>115</v>
+      </c>
+      <c r="C17" s="58"/>
+      <c r="D17" s="58"/>
+    </row>
+    <row r="19" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="51" t="n">
+        <v>2</v>
+      </c>
+      <c r="B19" s="52" t="s">
+        <v>116</v>
+      </c>
+      <c r="C19" s="52"/>
+      <c r="D19" s="52"/>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="53" t="s">
+        <v>117</v>
+      </c>
+      <c r="B20" s="53"/>
+      <c r="C20" s="53"/>
+      <c r="D20" s="53"/>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="54" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B22" s="55" t="s">
+        <v>118</v>
+      </c>
+      <c r="C22" s="55"/>
+      <c r="D22" s="56" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B23" s="55" t="s">
+        <v>119</v>
+      </c>
+      <c r="C23" s="55"/>
+      <c r="D23" s="56" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B24" s="55" t="s">
+        <v>120</v>
+      </c>
+      <c r="C24" s="55"/>
+      <c r="D24" s="56" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B25" s="55" t="s">
+        <v>122</v>
+      </c>
+      <c r="C25" s="55"/>
+      <c r="D25" s="56" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B26" s="55" t="s">
+        <v>124</v>
+      </c>
+      <c r="C26" s="55"/>
+      <c r="D26" s="56" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B27" s="55" t="s">
+        <v>126</v>
+      </c>
+      <c r="C27" s="55"/>
+      <c r="D27" s="56" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="54" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="B29" s="58" t="s">
+        <v>128</v>
+      </c>
+      <c r="C29" s="58"/>
+      <c r="D29" s="58"/>
+    </row>
+    <row r="30" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="57" t="n">
+        <v>2</v>
+      </c>
+      <c r="B30" s="58" t="s">
+        <v>129</v>
+      </c>
+      <c r="C30" s="58"/>
+      <c r="D30" s="58"/>
+    </row>
+    <row r="31" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="57" t="n">
+        <v>3</v>
+      </c>
+      <c r="B31" s="58" t="s">
+        <v>130</v>
+      </c>
+      <c r="C31" s="58"/>
+      <c r="D31" s="58"/>
+    </row>
+    <row r="32" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="57" t="n">
+        <v>4</v>
+      </c>
+      <c r="B32" s="58" t="s">
+        <v>131</v>
+      </c>
+      <c r="C32" s="58"/>
+      <c r="D32" s="58"/>
+    </row>
+    <row r="33" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="57" t="n">
+        <v>5</v>
+      </c>
+      <c r="B33" s="58" t="s">
+        <v>132</v>
+      </c>
+      <c r="C33" s="58"/>
+      <c r="D33" s="58"/>
+    </row>
+    <row r="35" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="51" t="n">
+        <v>3</v>
+      </c>
+      <c r="B35" s="52" t="s">
+        <v>133</v>
+      </c>
+      <c r="C35" s="52"/>
+      <c r="D35" s="52"/>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="53" t="s">
+        <v>134</v>
+      </c>
+      <c r="B36" s="53"/>
+      <c r="C36" s="53"/>
+      <c r="D36" s="53"/>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="54" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B38" s="55" t="s">
+        <v>100</v>
+      </c>
+      <c r="C38" s="55"/>
+      <c r="D38" s="56" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B39" s="55" t="s">
+        <v>136</v>
+      </c>
+      <c r="C39" s="55"/>
+      <c r="D39" s="56" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B40" s="55" t="s">
+        <v>137</v>
+      </c>
+      <c r="C40" s="55"/>
+      <c r="D40" s="56" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B41" s="55" t="s">
+        <v>139</v>
+      </c>
+      <c r="C41" s="55"/>
+      <c r="D41" s="56" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B42" s="55" t="s">
+        <v>141</v>
+      </c>
+      <c r="C42" s="55"/>
+      <c r="D42" s="56" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="54" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="B44" s="58" t="s">
+        <v>142</v>
+      </c>
+      <c r="C44" s="58"/>
+      <c r="D44" s="58"/>
+    </row>
+    <row r="45" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="57" t="n">
+        <v>2</v>
+      </c>
+      <c r="B45" s="58" t="s">
+        <v>143</v>
+      </c>
+      <c r="C45" s="58"/>
+      <c r="D45" s="58"/>
+    </row>
+    <row r="46" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="57" t="n">
+        <v>3</v>
+      </c>
+      <c r="B46" s="58" t="s">
+        <v>144</v>
+      </c>
+      <c r="C46" s="58"/>
+      <c r="D46" s="58"/>
+    </row>
+    <row r="47" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="57" t="n">
+        <v>4</v>
+      </c>
+      <c r="B47" s="58" t="s">
+        <v>145</v>
+      </c>
+      <c r="C47" s="58"/>
+      <c r="D47" s="58"/>
+    </row>
+    <row r="49" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="51" t="n">
+        <v>4</v>
+      </c>
+      <c r="B49" s="52" t="s">
+        <v>146</v>
+      </c>
+      <c r="C49" s="52"/>
+      <c r="D49" s="52"/>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="53" t="s">
+        <v>147</v>
+      </c>
+      <c r="B50" s="53"/>
+      <c r="C50" s="53"/>
+      <c r="D50" s="53"/>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A51" s="54" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B52" s="55" t="s">
+        <v>148</v>
+      </c>
+      <c r="C52" s="55"/>
+      <c r="D52" s="56" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B53" s="55" t="s">
+        <v>150</v>
+      </c>
+      <c r="C53" s="55"/>
+      <c r="D53" s="56" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B54" s="55" t="s">
+        <v>152</v>
+      </c>
+      <c r="C54" s="55"/>
+      <c r="D54" s="56" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B55" s="55" t="s">
+        <v>153</v>
+      </c>
+      <c r="C55" s="55"/>
+      <c r="D55" s="56" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B56" s="55" t="s">
+        <v>154</v>
+      </c>
+      <c r="C56" s="55"/>
+      <c r="D56" s="56" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A57" s="54" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A58" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="B58" s="58" t="s">
+        <v>155</v>
+      </c>
+      <c r="C58" s="58"/>
+      <c r="D58" s="58"/>
+    </row>
+    <row r="59" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A59" s="57" t="n">
+        <v>2</v>
+      </c>
+      <c r="B59" s="58" t="s">
+        <v>156</v>
+      </c>
+      <c r="C59" s="58"/>
+      <c r="D59" s="58"/>
+    </row>
+    <row r="60" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A60" s="57" t="n">
+        <v>3</v>
+      </c>
+      <c r="B60" s="58" t="s">
+        <v>157</v>
+      </c>
+      <c r="C60" s="58"/>
+      <c r="D60" s="58"/>
+    </row>
+    <row r="61" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A61" s="57" t="n">
+        <v>4</v>
+      </c>
+      <c r="B61" s="58" t="s">
+        <v>158</v>
+      </c>
+      <c r="C61" s="58"/>
+      <c r="D61" s="58"/>
+    </row>
+    <row r="62" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A62" s="57" t="n">
+        <v>5</v>
+      </c>
+      <c r="B62" s="58" t="s">
+        <v>159</v>
+      </c>
+      <c r="C62" s="58"/>
+      <c r="D62" s="58"/>
+    </row>
+    <row r="64" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A64" s="51" t="n">
+        <v>5</v>
+      </c>
+      <c r="B64" s="52" t="s">
+        <v>160</v>
+      </c>
+      <c r="C64" s="52"/>
+      <c r="D64" s="52"/>
+    </row>
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A65" s="53" t="s">
+        <v>161</v>
+      </c>
+      <c r="B65" s="53"/>
+      <c r="C65" s="53"/>
+      <c r="D65" s="53"/>
+    </row>
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A66" s="54" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B67" s="55" t="s">
+        <v>162</v>
+      </c>
+      <c r="C67" s="55"/>
+      <c r="D67" s="56" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B68" s="55" t="s">
+        <v>164</v>
+      </c>
+      <c r="C68" s="55"/>
+      <c r="D68" s="56" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B69" s="55" t="s">
+        <v>165</v>
+      </c>
+      <c r="C69" s="55"/>
+      <c r="D69" s="56" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B70" s="55" t="s">
+        <v>167</v>
+      </c>
+      <c r="C70" s="55"/>
+      <c r="D70" s="56" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B71" s="55" t="s">
+        <v>168</v>
+      </c>
+      <c r="C71" s="55"/>
+      <c r="D71" s="56" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A72" s="54" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A73" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="B73" s="58" t="s">
+        <v>169</v>
+      </c>
+      <c r="C73" s="58"/>
+      <c r="D73" s="58"/>
+    </row>
+    <row r="74" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A74" s="57" t="n">
+        <v>2</v>
+      </c>
+      <c r="B74" s="58" t="s">
+        <v>170</v>
+      </c>
+      <c r="C74" s="58"/>
+      <c r="D74" s="58"/>
+    </row>
+    <row r="75" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A75" s="57" t="n">
+        <v>3</v>
+      </c>
+      <c r="B75" s="58" t="s">
+        <v>171</v>
+      </c>
+      <c r="C75" s="58"/>
+      <c r="D75" s="58"/>
+    </row>
+    <row r="76" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A76" s="57" t="n">
+        <v>4</v>
+      </c>
+      <c r="B76" s="58" t="s">
+        <v>172</v>
+      </c>
+      <c r="C76" s="58"/>
+      <c r="D76" s="58"/>
+    </row>
+    <row r="77" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A77" s="57" t="n">
+        <v>5</v>
+      </c>
+      <c r="B77" s="58" t="s">
+        <v>173</v>
+      </c>
+      <c r="C77" s="58"/>
+      <c r="D77" s="58"/>
+    </row>
+    <row r="79" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A79" s="51" t="n">
+        <v>6</v>
+      </c>
+      <c r="B79" s="52" t="s">
+        <v>174</v>
+      </c>
+      <c r="C79" s="52"/>
+      <c r="D79" s="52"/>
+    </row>
+    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A80" s="53" t="s">
+        <v>175</v>
+      </c>
+      <c r="B80" s="53"/>
+      <c r="C80" s="53"/>
+      <c r="D80" s="53"/>
+    </row>
+    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A81" s="54" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B82" s="55" t="s">
+        <v>176</v>
+      </c>
+      <c r="C82" s="55"/>
+      <c r="D82" s="56" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B83" s="55" t="s">
+        <v>177</v>
+      </c>
+      <c r="C83" s="55"/>
+      <c r="D83" s="56" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B84" s="55" t="s">
+        <v>141</v>
+      </c>
+      <c r="C84" s="55"/>
+      <c r="D84" s="56" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B85" s="55" t="s">
+        <v>179</v>
+      </c>
+      <c r="C85" s="55"/>
+      <c r="D85" s="56" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B86" s="55" t="s">
+        <v>180</v>
+      </c>
+      <c r="C86" s="55"/>
+      <c r="D86" s="56" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A87" s="54" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="88" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A88" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="B88" s="58" t="s">
+        <v>182</v>
+      </c>
+      <c r="C88" s="58"/>
+      <c r="D88" s="58"/>
+    </row>
+    <row r="89" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A89" s="57" t="n">
+        <v>2</v>
+      </c>
+      <c r="B89" s="58" t="s">
+        <v>183</v>
+      </c>
+      <c r="C89" s="58"/>
+      <c r="D89" s="58"/>
+    </row>
+    <row r="90" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A90" s="57" t="n">
+        <v>3</v>
+      </c>
+      <c r="B90" s="58" t="s">
+        <v>184</v>
+      </c>
+      <c r="C90" s="58"/>
+      <c r="D90" s="58"/>
+    </row>
+    <row r="92" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A92" s="51" t="n">
+        <v>7</v>
+      </c>
+      <c r="B92" s="52" t="s">
+        <v>185</v>
+      </c>
+      <c r="C92" s="52"/>
+      <c r="D92" s="52"/>
+    </row>
+    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A93" s="53" t="s">
+        <v>186</v>
+      </c>
+      <c r="B93" s="53"/>
+      <c r="C93" s="53"/>
+      <c r="D93" s="53"/>
+    </row>
+    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A94" s="54" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B95" s="55" t="s">
+        <v>187</v>
+      </c>
+      <c r="C95" s="55"/>
+      <c r="D95" s="56" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B96" s="55" t="s">
+        <v>189</v>
+      </c>
+      <c r="C96" s="55"/>
+      <c r="D96" s="56" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B97" s="55" t="s">
+        <v>190</v>
+      </c>
+      <c r="C97" s="55"/>
+      <c r="D97" s="56" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B98" s="55" t="s">
+        <v>191</v>
+      </c>
+      <c r="C98" s="55"/>
+      <c r="D98" s="56" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A99" s="54" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="100" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A100" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="B100" s="58" t="s">
+        <v>193</v>
+      </c>
+      <c r="C100" s="58"/>
+      <c r="D100" s="58"/>
+    </row>
+    <row r="101" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A101" s="57" t="n">
+        <v>2</v>
+      </c>
+      <c r="B101" s="58" t="s">
+        <v>194</v>
+      </c>
+      <c r="C101" s="58"/>
+      <c r="D101" s="58"/>
+    </row>
+    <row r="102" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A102" s="57" t="n">
+        <v>3</v>
+      </c>
+      <c r="B102" s="58" t="s">
+        <v>195</v>
+      </c>
+      <c r="C102" s="58"/>
+      <c r="D102" s="58"/>
+    </row>
+    <row r="103" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A103" s="57" t="n">
+        <v>4</v>
+      </c>
+      <c r="B103" s="58" t="s">
+        <v>196</v>
+      </c>
+      <c r="C103" s="58"/>
+      <c r="D103" s="58"/>
+    </row>
+    <row r="105" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A105" s="51" t="n">
+        <v>8</v>
+      </c>
+      <c r="B105" s="52" t="s">
+        <v>197</v>
+      </c>
+      <c r="C105" s="52"/>
+      <c r="D105" s="52"/>
+    </row>
+    <row r="106" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A106" s="53" t="s">
+        <v>198</v>
+      </c>
+      <c r="B106" s="53"/>
+      <c r="C106" s="53"/>
+      <c r="D106" s="53"/>
+    </row>
+    <row r="107" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A107" s="54" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="108" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B108" s="55" t="s">
+        <v>199</v>
+      </c>
+      <c r="C108" s="55"/>
+      <c r="D108" s="56" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="109" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B109" s="55" t="s">
+        <v>200</v>
+      </c>
+      <c r="C109" s="55"/>
+      <c r="D109" s="56" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="110" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B110" s="55" t="s">
+        <v>202</v>
+      </c>
+      <c r="C110" s="55"/>
+      <c r="D110" s="56" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="111" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B111" s="55" t="s">
+        <v>203</v>
+      </c>
+      <c r="C111" s="55"/>
+      <c r="D111" s="56" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="112" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B112" s="55" t="s">
+        <v>205</v>
+      </c>
+      <c r="C112" s="55"/>
+      <c r="D112" s="56" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="113" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A113" s="54" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="114" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A114" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="B114" s="58" t="s">
+        <v>206</v>
+      </c>
+      <c r="C114" s="58"/>
+      <c r="D114" s="58"/>
+    </row>
+    <row r="115" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A115" s="57" t="n">
+        <v>2</v>
+      </c>
+      <c r="B115" s="58" t="s">
+        <v>207</v>
+      </c>
+      <c r="C115" s="58"/>
+      <c r="D115" s="58"/>
+    </row>
+    <row r="116" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A116" s="57" t="n">
+        <v>3</v>
+      </c>
+      <c r="B116" s="58" t="s">
+        <v>208</v>
+      </c>
+      <c r="C116" s="58"/>
+      <c r="D116" s="58"/>
+    </row>
+    <row r="117" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A117" s="57" t="n">
+        <v>4</v>
+      </c>
+      <c r="B117" s="58" t="s">
+        <v>209</v>
+      </c>
+      <c r="C117" s="58"/>
+      <c r="D117" s="58"/>
+    </row>
+    <row r="118" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A118" s="57" t="n">
+        <v>5</v>
+      </c>
+      <c r="B118" s="58" t="s">
+        <v>210</v>
+      </c>
+      <c r="C118" s="58"/>
+      <c r="D118" s="58"/>
+    </row>
+    <row r="120" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A120" s="51" t="n">
+        <v>9</v>
+      </c>
+      <c r="B120" s="52" t="s">
+        <v>211</v>
+      </c>
+      <c r="C120" s="52"/>
+      <c r="D120" s="52"/>
+    </row>
+    <row r="121" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A121" s="53" t="s">
+        <v>212</v>
+      </c>
+      <c r="B121" s="53"/>
+      <c r="C121" s="53"/>
+      <c r="D121" s="53"/>
+    </row>
+    <row r="122" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A122" s="54" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="123" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B123" s="55" t="s">
+        <v>139</v>
+      </c>
+      <c r="C123" s="55"/>
+      <c r="D123" s="56" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="124" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B124" s="55" t="s">
+        <v>214</v>
+      </c>
+      <c r="C124" s="55"/>
+      <c r="D124" s="56" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="125" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B125" s="55" t="s">
+        <v>215</v>
+      </c>
+      <c r="C125" s="55"/>
+      <c r="D125" s="56" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="126" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B126" s="55" t="s">
+        <v>216</v>
+      </c>
+      <c r="C126" s="55"/>
+      <c r="D126" s="56" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="127" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B127" s="55" t="s">
+        <v>217</v>
+      </c>
+      <c r="C127" s="55"/>
+      <c r="D127" s="56" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="128" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A128" s="54" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="129" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A129" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="B129" s="58" t="s">
+        <v>219</v>
+      </c>
+      <c r="C129" s="58"/>
+      <c r="D129" s="58"/>
+    </row>
+    <row r="130" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A130" s="57" t="n">
+        <v>2</v>
+      </c>
+      <c r="B130" s="58" t="s">
+        <v>220</v>
+      </c>
+      <c r="C130" s="58"/>
+      <c r="D130" s="58"/>
+    </row>
+    <row r="131" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A131" s="57" t="n">
+        <v>3</v>
+      </c>
+      <c r="B131" s="58" t="s">
+        <v>221</v>
+      </c>
+      <c r="C131" s="58"/>
+      <c r="D131" s="58"/>
+    </row>
+    <row r="132" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A132" s="57" t="n">
+        <v>4</v>
+      </c>
+      <c r="B132" s="58" t="s">
+        <v>222</v>
+      </c>
+      <c r="C132" s="58"/>
+      <c r="D132" s="58"/>
+    </row>
+    <row r="134" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A134" s="51" t="n">
+        <v>10</v>
+      </c>
+      <c r="B134" s="52" t="s">
+        <v>223</v>
+      </c>
+      <c r="C134" s="52"/>
+      <c r="D134" s="52"/>
+    </row>
+    <row r="135" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A135" s="53" t="s">
+        <v>224</v>
+      </c>
+      <c r="B135" s="53"/>
+      <c r="C135" s="53"/>
+      <c r="D135" s="53"/>
+    </row>
+    <row r="136" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A136" s="54" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="137" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B137" s="55" t="s">
+        <v>225</v>
+      </c>
+      <c r="C137" s="55"/>
+      <c r="D137" s="56" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="138" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B138" s="55" t="s">
+        <v>227</v>
+      </c>
+      <c r="C138" s="55"/>
+      <c r="D138" s="56" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="139" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B139" s="55" t="s">
+        <v>228</v>
+      </c>
+      <c r="C139" s="55"/>
+      <c r="D139" s="56" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="140" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B140" s="55" t="s">
+        <v>229</v>
+      </c>
+      <c r="C140" s="55"/>
+      <c r="D140" s="56" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="141" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A141" s="54" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="142" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A142" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="B142" s="58" t="s">
+        <v>231</v>
+      </c>
+      <c r="C142" s="58"/>
+      <c r="D142" s="58"/>
+    </row>
+    <row r="143" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A143" s="57" t="n">
+        <v>2</v>
+      </c>
+      <c r="B143" s="58" t="s">
+        <v>232</v>
+      </c>
+      <c r="C143" s="58"/>
+      <c r="D143" s="58"/>
+    </row>
+    <row r="144" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A144" s="57" t="n">
+        <v>3</v>
+      </c>
+      <c r="B144" s="58" t="s">
+        <v>233</v>
+      </c>
+      <c r="C144" s="58"/>
+      <c r="D144" s="58"/>
+    </row>
+    <row r="145" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A145" s="57" t="n">
+        <v>4</v>
+      </c>
+      <c r="B145" s="58" t="s">
+        <v>234</v>
+      </c>
+      <c r="C145" s="58"/>
+      <c r="D145" s="58"/>
+    </row>
+  </sheetData>
+  <mergeCells count="114">
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="A5:D5"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="A20:D20"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="B33:D33"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="A36:D36"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="B44:D44"/>
+    <mergeCell ref="B45:D45"/>
+    <mergeCell ref="B46:D46"/>
+    <mergeCell ref="B47:D47"/>
+    <mergeCell ref="B49:D49"/>
+    <mergeCell ref="A50:D50"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="B54:C54"/>
+    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="B58:D58"/>
+    <mergeCell ref="B59:D59"/>
+    <mergeCell ref="B60:D60"/>
+    <mergeCell ref="B61:D61"/>
+    <mergeCell ref="B62:D62"/>
+    <mergeCell ref="B64:D64"/>
+    <mergeCell ref="A65:D65"/>
+    <mergeCell ref="B67:C67"/>
+    <mergeCell ref="B68:C68"/>
+    <mergeCell ref="B69:C69"/>
+    <mergeCell ref="B70:C70"/>
+    <mergeCell ref="B71:C71"/>
+    <mergeCell ref="B73:D73"/>
+    <mergeCell ref="B74:D74"/>
+    <mergeCell ref="B75:D75"/>
+    <mergeCell ref="B76:D76"/>
+    <mergeCell ref="B77:D77"/>
+    <mergeCell ref="B79:D79"/>
+    <mergeCell ref="A80:D80"/>
+    <mergeCell ref="B82:C82"/>
+    <mergeCell ref="B83:C83"/>
+    <mergeCell ref="B84:C84"/>
+    <mergeCell ref="B85:C85"/>
+    <mergeCell ref="B86:C86"/>
+    <mergeCell ref="B88:D88"/>
+    <mergeCell ref="B89:D89"/>
+    <mergeCell ref="B90:D90"/>
+    <mergeCell ref="B92:D92"/>
+    <mergeCell ref="A93:D93"/>
+    <mergeCell ref="B95:C95"/>
+    <mergeCell ref="B96:C96"/>
+    <mergeCell ref="B97:C97"/>
+    <mergeCell ref="B98:C98"/>
+    <mergeCell ref="B100:D100"/>
+    <mergeCell ref="B101:D101"/>
+    <mergeCell ref="B102:D102"/>
+    <mergeCell ref="B103:D103"/>
+    <mergeCell ref="B105:D105"/>
+    <mergeCell ref="A106:D106"/>
+    <mergeCell ref="B108:C108"/>
+    <mergeCell ref="B109:C109"/>
+    <mergeCell ref="B110:C110"/>
+    <mergeCell ref="B111:C111"/>
+    <mergeCell ref="B112:C112"/>
+    <mergeCell ref="B114:D114"/>
+    <mergeCell ref="B115:D115"/>
+    <mergeCell ref="B116:D116"/>
+    <mergeCell ref="B117:D117"/>
+    <mergeCell ref="B118:D118"/>
+    <mergeCell ref="B120:D120"/>
+    <mergeCell ref="A121:D121"/>
+    <mergeCell ref="B123:C123"/>
+    <mergeCell ref="B124:C124"/>
+    <mergeCell ref="B125:C125"/>
+    <mergeCell ref="B126:C126"/>
+    <mergeCell ref="B127:C127"/>
+    <mergeCell ref="B129:D129"/>
+    <mergeCell ref="B130:D130"/>
+    <mergeCell ref="B131:D131"/>
+    <mergeCell ref="B132:D132"/>
+    <mergeCell ref="B134:D134"/>
+    <mergeCell ref="A135:D135"/>
+    <mergeCell ref="B137:C137"/>
+    <mergeCell ref="B138:C138"/>
+    <mergeCell ref="B139:C139"/>
+    <mergeCell ref="B140:C140"/>
+    <mergeCell ref="B142:D142"/>
+    <mergeCell ref="B143:D143"/>
+    <mergeCell ref="B144:D144"/>
+    <mergeCell ref="B145:D145"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
 </file>
--- a/tracker-nl.xlsx
+++ b/tracker-nl.xlsx
@@ -1694,7 +1694,7 @@
       </c>
       <c r="F5" s="69" t="n"/>
       <c r="G5" s="71">
-        <f>IF(N3="","",IF(N3&lt;-0.01,"! Te snel",IF(N3&lt;-0.003,"✓ Op koers",IF(N3&lt;=0.003,"– Stabiel",IF(N3&lt;=0.01,"✓ Op koers","! Te snel")))))</f>
+        <f>IF(OR(N1="",N2=""),"",IF(N2/N1*1000&lt;-10,"⚠ Too fast",IF(N2/N1*1000&lt;-3,"✓ On track",IF(N2/N1*1000&lt;=3,"– Stable",IF(N2/N1*1000&lt;=10,"✓ On track","⚠ Too fast")))))</f>
         <v/>
       </c>
       <c r="I5" s="69" t="n"/>
@@ -3202,7 +3202,7 @@
         </is>
       </c>
       <c r="G5" s="110">
-        <f>IF(COUNT(B4:B30)&gt;=1,INDEX(B4:B30,COUNT(B4:B30)),"")</f>
+        <f>IF(COUNT(Gewicht!$B$4:$B$30)&gt;=1,INDEX(Gewicht!$B$4:$B$30,COUNT(Gewicht!$B$4:$B$30)),"")</f>
         <v/>
       </c>
     </row>
